--- a/02_加值成品/八下/八下6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-1 力的作用與表示　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下6-1 力的作用與表示　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>力能改變物體的什麼？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>合力方向指向較大力的一方</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>運動狀態或形狀</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>會,如作用點不同轉動效果不同</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不一定,可能等速運動</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>效果</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>力的單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>相減</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>牛頓(N)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>大小</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>箭號(力圖)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>力的三要素是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不一定,可能等速運動</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>施力同時受反作用力</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>會,如作用點不同轉動效果不同</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>大小方向作用點</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>三項</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>力常用什麼表示？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>箭號(力圖)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>捏黏土;推車</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>相互</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>箭號長度代表力的？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>大小</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>牛頓N</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>箭號起點</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>量</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>同一直線同向兩力合力如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>捏黏土;推車</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>相減</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>牛頓(N)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>同向</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>同一直線反向兩力合力如何？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>捏黏土;推車</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>形狀</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>相減</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反向</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>力是相互的還單方的？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>箭號(力圖)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>大小</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>相互</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>力可改變物體的運動狀態或？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>運動狀態</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>形狀</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>牛頓(N)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>效果</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>力的大小單位是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>箭號(力圖)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>形狀</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>牛頓N</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>相減</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-1 力的作用與表示　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下6-1 力的作用與表示　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>5N向右與3N向右合力？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0N(平衡)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>2N向右</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>8N向右</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>7N向東</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>5N向右與3N向左合力？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>2N向右</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>0N</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>9N向右</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>相減</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>力圖箭頭代表？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>相互</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>合力為零</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>方向</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>向量</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>壓扁黏土是力改變？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>作用效果</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>形狀</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>箭號(力圖)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>捏黏土;推車</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>變形</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>推動靜止物體是力改變？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>形狀</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>作用效果</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>運動狀態</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>由靜到動</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>4N向左與4N向右合力？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>7N向東</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>0N(平衡)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>9N向右</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>抵消</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>力的作用點畫在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>運動狀態</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>箭號(力圖)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>箭號起點</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>施力處</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>力看不見我們如何知道有力？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>箭號(力圖)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>牛頓N</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>由其效果</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>牛頓(N)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>觀察</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>7N向右與2N向右合力？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>9N向右</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>往8N方</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>0N(平衡)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>相加</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>3N向東與3N向西合力？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>7N向東</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>0N</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>9N向右</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>抵消</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-1 力的作用與表示　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下6-1 力的作用與表示　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>拔河兩隊各出力用合力解釋勝負？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>合力方向指向較大力的一方</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>不一定,可能等速運動</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>施力同時受反作用力</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>運動狀態或形狀</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>合力</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何說力是相互作用？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>大小方向作用點</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>施力同時受反作用力</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不一定,可能等速運動</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>向下箭號長度按比例</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>牛頓三律</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>6N向東3N向東2N向西合力？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>7N向東</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>2N向右</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0N(平衡)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>向量和</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>三要素改變其一效果會變嗎?舉例</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>會,如作用點不同轉動效果不同</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>不一定,可能等速運動</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>向下箭號長度按比例</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>合力方向指向較大力的一方</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>要素</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>合力為零物體一定靜止嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>不一定,可能等速運動</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>施力同時受反作用力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>運動狀態或形狀</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>合力方向指向較大力的一方</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>用箭號畫10N向下的重力如何表示？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>施力同時受反作用力</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>會,如作用點不同轉動效果不同</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>向下箭號長度按比例</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>合力方向指向較大力的一方</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>力圖</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>兩力大小相等方向相反作用同物體結果？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>合力為零</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>形狀</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>相減</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>大小</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>力改變形狀與運動的例子各一？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>牛頓N</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>相加</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>箭號起點</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>捏黏土;推車</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>效果</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>用力推牆牆微微形變說明力有？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>大小</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>形狀</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>作用效果</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>牛頓(N)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>作用</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>反向拉繩8N與5N繩往哪方移動？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>往8N方</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>0N(平衡)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>0N</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>合力</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>效果</t>
+          <t>效果：力作用在物體上，可能使物體的運動狀態(速度或方向)改變，也可能使物體產生形變，這是力的兩種基本作用效果</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：國際單位制中，力的大小單位是牛頓，符號寫作N</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>三項</t>
+          <t>三項：完整描述一個力需要三個要素：力的大小、方向、以及作用點</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：力有大小也有方向，屬於向量，常用箭號來表示，箭號長度代表大小、箭頭方向代表力的方向</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>量</t>
+          <t>量：畫力的圖示時用箭頭長度表示力的大小，箭頭方向表示力的方向</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>同向</t>
+          <t>同向：兩個力方向相同時，合力等於兩力大小直接相加，方向與原方向相同</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反向</t>
+          <t>反向：兩個力方向相反時，合力等於較大的力減去較小的力，方向與較大的力相同</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：力的作用一定是相互的，一個物體施力給另一個物體時，同時也會受到對方大小相等、方向相反的反作用力</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>效果</t>
+          <t>效果：力作用在物體上，除了可能改變物體的運動狀態（速度、方向），也可能使物體產生形變，這些都是力的作用效果</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>單位：國際單位制中，力的大小單位是牛頓，符號寫作N</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：兩力方向相同可直接相加，5牛頓加3牛頓等於8牛頓，方向仍向右</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>相減</t>
+          <t>相減：兩力方向相反，合力等於較大的力減去較小的力，5減3等於2牛頓，方向與較大的力(向右)相同</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>向量</t>
+          <t>向量：力圖中箭頭所指的方向就代表這個力作用的方向，箭號長度則代表力的大小</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>變形</t>
+          <t>變形：用力壓黏土使它從原本的形狀變成扁平狀，這是力使物體產生形變的效果</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>由靜到動</t>
+          <t>由靜到動：原本靜止的物體受到推力後開始移動，這是力使物體運動狀態改變的效果</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>抵消</t>
+          <t>抵消：兩力大小相等、方向相反，合力等於兩者相減為0，彼此互相抵消，物體處於力平衡狀態</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>施力處</t>
+          <t>施力處：畫力圖時，箭號的起點要放在力實際施加的位置(作用點)上</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>觀察</t>
+          <t>觀察：力本身看不見摸不著，但可以透過觀察物體運動狀態的改變或形狀的改變，間接推知有力的作用</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：兩個力方向相同時可以直接相加，7牛頓加2牛頓等於9牛頓，方向仍然向右</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>抵消</t>
+          <t>抵消：兩個大小相等、方向相反的力作用在同一物體上，會互相抵消，合力等於0</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>合力</t>
+          <t>合力：拔河繩子受到兩隊方向相反的拉力，合力等於較大力減去較小力，繩子(和人)會被拉向合力方向，也就是出力較大的那一隊獲勝</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>牛頓三律</t>
+          <t>牛頓三律：根據牛頓第三運動定律，一個物體施力給另一個物體的同時，一定會受到對方大小相等、方向相反的反作用力，兩者是成對同時發生的，所以力是相互作用</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>向量和</t>
+          <t>向量和：先把同方向的力相加，向東的6N加3N等於9N向東，再和2N向西相減，9減2等於7N向東</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>要素</t>
+          <t>要素：力的大小、方向、作用點只要有一個改變，力產生的效果就可能不同，例如同樣大小方向的力，作用在門的不同位置，開門所需的施力感受或轉動效果就不一樣</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：根據牛頓第一運動定律，合力為零時物體會維持原本的運動狀態，可能是靜止，也可能是持續做等速度直線運動，不一定是靜止</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>力圖</t>
+          <t>力圖：畫力圖時，箭號要指向下方(代表重力方向)，箭號的長度要依照選定的比例尺畫成對應10牛頓大小的長度</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：兩力大小相等、方向相反時，合力等於兩者相減為零，物體處於力平衡的狀態</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>效果</t>
+          <t>效果：捏黏土使黏土形狀改變，是力改變形狀的例子；推車使靜止的車子開始移動，是力改變運動狀態的例子</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>作用</t>
+          <t>作用：即使牆壁看起來沒有移動，用力推牆仍然會使牆壁產生極微小的形變，這證明力確實對物體產生了作用效果，只是形變量太小不容易察覺</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>合力</t>
+          <t>合力：兩邊力方向相反時，合力等於較大的力減去較小的力，8牛頓比5牛頓大，所以繩子會往施力較大(8N)的那一方移動</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下6-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-1_三種難度測驗卷.xlsx
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>7N向東</t>
+          <t>往8N方</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>8N向右</t>
+          <t>9N向右</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>9N向右</t>
+          <t>2N向右</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
+          <t>8N向右</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>0N</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>7N向東</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>0N</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>8N向右</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
